--- a/- Hash Perceptual.xlsx
+++ b/- Hash Perceptual.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925DECDC-BCEF-463F-9D0B-83CD01AA6CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2799856-F875-462B-8EE0-FC15E6032E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="22" r:id="rId1"/>
     <sheet name="WashingtonDatabase" sheetId="2" r:id="rId2"/>
+    <sheet name="MountainDatabase" sheetId="23" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">LennaDatabase!$A$1:$B$1</definedName>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="227">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -664,6 +665,63 @@
   </si>
   <si>
     <t>CPR Hash 10</t>
+  </si>
+  <si>
+    <t>ffffc7cb01000000</t>
+  </si>
+  <si>
+    <t>Alternative (1)</t>
+  </si>
+  <si>
+    <t>b9c4c65a8bd15c3c</t>
+  </si>
+  <si>
+    <t>b9c4d65a8b515c3c</t>
+  </si>
+  <si>
+    <t>402416531b191a1f</t>
+  </si>
+  <si>
+    <t>402416531b391a1b</t>
+  </si>
+  <si>
+    <t>ffffd7eb8b000000</t>
+  </si>
+  <si>
+    <t>ffffd7cb8b800000</t>
+  </si>
+  <si>
+    <t>03640002000</t>
+  </si>
+  <si>
+    <t>000100002c0</t>
+  </si>
+  <si>
+    <t>00442616175b3b19</t>
+  </si>
+  <si>
+    <t>0050243616535b3b</t>
+  </si>
+  <si>
+    <t>a5e7b2edccfcfade</t>
+  </si>
+  <si>
+    <t>d1c08489ccdcf171</t>
+  </si>
+  <si>
+    <t>c7d7f13858c4ee02</t>
+  </si>
+  <si>
+    <t>2616531b3b181a1b</t>
+  </si>
+  <si>
+    <t>2246cc2d3a56cd91</t>
+  </si>
+  <si>
+    <t>849c4c481e9d2636</t>
+  </si>
+  <si>
+    <t>2616531b3b181e1b</t>
   </si>
 </sst>
 </file>
@@ -770,7 +828,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -787,6 +845,9 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2477,4 +2538,394 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977491FD-2608-4368-88A1-010C2609C8BB}">
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="7"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="7"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="7"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="7"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="7"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="7"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="7"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="7"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="7"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="7"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="12"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="12"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="7"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="12"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="7"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/- Hash Perceptual.xlsx
+++ b/- Hash Perceptual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2799856-F875-462B-8EE0-FC15E6032E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F925972B-EC56-45A6-AA53-542E29DA9B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="261">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -722,6 +722,108 @@
   </si>
   <si>
     <t>2616531b3b181e1b</t>
+  </si>
+  <si>
+    <t>Alternative (2)</t>
+  </si>
+  <si>
+    <t>Alternative (3)</t>
+  </si>
+  <si>
+    <t>Alternative (4)</t>
+  </si>
+  <si>
+    <t>Alternative (5)</t>
+  </si>
+  <si>
+    <t>Alternative (6)</t>
+  </si>
+  <si>
+    <t>Alternative (7)</t>
+  </si>
+  <si>
+    <t>Alternative (8)</t>
+  </si>
+  <si>
+    <t>Alternative (9)</t>
+  </si>
+  <si>
+    <t>Alternative (10)</t>
+  </si>
+  <si>
+    <t>Alternative (11)</t>
+  </si>
+  <si>
+    <t>Alternative (12)</t>
+  </si>
+  <si>
+    <t>Alternative (13)</t>
+  </si>
+  <si>
+    <t>Alternative (14)</t>
+  </si>
+  <si>
+    <t>Alternative (15)</t>
+  </si>
+  <si>
+    <t>Alternative (16)</t>
+  </si>
+  <si>
+    <t>Alternative (17)</t>
+  </si>
+  <si>
+    <t>Alternative (18)</t>
+  </si>
+  <si>
+    <t>Alternative (19)</t>
+  </si>
+  <si>
+    <t>Alternative (20)</t>
+  </si>
+  <si>
+    <t>Alternative (21)</t>
+  </si>
+  <si>
+    <t>Alternative (22)</t>
+  </si>
+  <si>
+    <t>Alternative (23)</t>
+  </si>
+  <si>
+    <t>Alternative (24)</t>
+  </si>
+  <si>
+    <t>Alternative (25)</t>
+  </si>
+  <si>
+    <t>Alternative (26)</t>
+  </si>
+  <si>
+    <t>Alternative (27)</t>
+  </si>
+  <si>
+    <t>Alternative (28)</t>
+  </si>
+  <si>
+    <t>Alternative (29)</t>
+  </si>
+  <si>
+    <t>Alternative (30)</t>
+  </si>
+  <si>
+    <t>402416531b191a1b</t>
+  </si>
+  <si>
+    <t>08010000080</t>
+  </si>
+  <si>
+    <t>0018264381297920</t>
+  </si>
+  <si>
+    <t>08010001080</t>
+  </si>
+  <si>
+    <t>0440243616535b3b</t>
   </si>
 </sst>
 </file>
@@ -2542,7 +2644,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977491FD-2608-4368-88A1-010C2609C8BB}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -2550,7 +2652,7 @@
     <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -2673,35 +2775,85 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
+      <c r="A4" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
+      <c r="A5" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
+      <c r="A6" s="7" t="s">
+        <v>229</v>
+      </c>
       <c r="B6" s="2"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -2715,7 +2867,9 @@
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
+      <c r="A7" s="7" t="s">
+        <v>230</v>
+      </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -2729,7 +2883,9 @@
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
+      <c r="A8" s="7" t="s">
+        <v>231</v>
+      </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -2743,7 +2899,9 @@
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
+      <c r="A9" s="7" t="s">
+        <v>232</v>
+      </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -2757,7 +2915,9 @@
       <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
+      <c r="A10" s="7" t="s">
+        <v>233</v>
+      </c>
       <c r="B10" s="2"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -2771,7 +2931,9 @@
       <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
+      <c r="A11" s="7" t="s">
+        <v>234</v>
+      </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="12"/>
@@ -2785,7 +2947,9 @@
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
+      <c r="A12" s="7" t="s">
+        <v>235</v>
+      </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -2799,7 +2963,9 @@
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
+      <c r="A13" s="7" t="s">
+        <v>236</v>
+      </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -2813,7 +2979,9 @@
       <c r="L13" s="1"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
+      <c r="A14" s="7" t="s">
+        <v>237</v>
+      </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -2827,7 +2995,9 @@
       <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
+      <c r="A15" s="7" t="s">
+        <v>238</v>
+      </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -2841,7 +3011,9 @@
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
+      <c r="A16" s="7" t="s">
+        <v>239</v>
+      </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -2855,7 +3027,9 @@
       <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
+      <c r="A17" s="7" t="s">
+        <v>240</v>
+      </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -2869,7 +3043,9 @@
       <c r="L17" s="12"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
+      <c r="A18" s="7" t="s">
+        <v>241</v>
+      </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -2883,7 +3059,9 @@
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
+      <c r="A19" s="7" t="s">
+        <v>242</v>
+      </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -2897,7 +3075,9 @@
       <c r="L19" s="12"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
+      <c r="A20" s="7" t="s">
+        <v>243</v>
+      </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -2911,7 +3091,9 @@
       <c r="L20" s="12"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
+      <c r="A21" s="7" t="s">
+        <v>244</v>
+      </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -2924,6 +3106,182 @@
       <c r="K21" s="1"/>
       <c r="L21" s="12"/>
     </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="12"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="12"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="12"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="12"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="12"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="12"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="12"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="12"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="12"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="12"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/- Hash Perceptual.xlsx
+++ b/- Hash Perceptual.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F925972B-EC56-45A6-AA53-542E29DA9B3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7482CBD-530B-4ADC-BE8D-93A1EC7D0696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="22" r:id="rId1"/>
-    <sheet name="WashingtonDatabase" sheetId="2" r:id="rId2"/>
-    <sheet name="MountainDatabase" sheetId="23" r:id="rId3"/>
+    <sheet name="MountainDatabase" sheetId="23" r:id="rId2"/>
+    <sheet name="WashingtonDatabase" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">LennaDatabase!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">LennaDatabase!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="282">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -824,13 +824,76 @@
   </si>
   <si>
     <t>0440243616535b3b</t>
+  </si>
+  <si>
+    <t>08053001000</t>
+  </si>
+  <si>
+    <t>0804b001000</t>
+  </si>
+  <si>
+    <t>ffffc7cb0b000200</t>
+  </si>
+  <si>
+    <t>b9c6c68283f17c3c</t>
+  </si>
+  <si>
+    <t>002416531b399a3a</t>
+  </si>
+  <si>
+    <t>ffffc7cf0f000200</t>
+  </si>
+  <si>
+    <t>07380000000</t>
+  </si>
+  <si>
+    <t>b9c4d6528bd15c3c</t>
+  </si>
+  <si>
+    <t>09046001000</t>
+  </si>
+  <si>
+    <t>ffffc7cb8b808000</t>
+  </si>
+  <si>
+    <t>08058002000</t>
+  </si>
+  <si>
+    <t>08058003000</t>
+  </si>
+  <si>
+    <t>08052001000</t>
+  </si>
+  <si>
+    <t>08091001000</t>
+  </si>
+  <si>
+    <t>100c0009000</t>
+  </si>
+  <si>
+    <t>0808a001000</t>
+  </si>
+  <si>
+    <t>08098001000</t>
+  </si>
+  <si>
+    <t>ffffcfcf0b000200</t>
+  </si>
+  <si>
+    <t>b9e6c68283d17c3c</t>
+  </si>
+  <si>
+    <t>412416531b391a3f</t>
+  </si>
+  <si>
+    <t>00038000000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -852,8 +915,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -902,6 +971,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -930,7 +1005,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -952,6 +1027,10 @@
     <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2214,6 +2293,976 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977491FD-2608-4368-88A1-010C2609C8BB}">
+  <dimension ref="A1:L36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="12"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="12"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="12"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="12"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="12"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="12"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="12"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="12"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="12"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="12"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="12"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="12"/>
+    </row>
+    <row r="36" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="E36" s="15">
+        <v>8091001000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97718C6-A416-40C3-8D45-6453EFA375E9}">
   <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2640,650 +3689,4 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977491FD-2608-4368-88A1-010C2609C8BB}">
-  <dimension ref="A1:L32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>229</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="12"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="12"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="12"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="12"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="12"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="12"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="12"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="12"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="12"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="12"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="12"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="12"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="12"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="12"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="12"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/- Hash Perceptual.xlsx
+++ b/- Hash Perceptual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7482CBD-530B-4ADC-BE8D-93A1EC7D0696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3847AE68-66B9-4BDF-84B1-856B154D3E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="285">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -887,6 +887,15 @@
   </si>
   <si>
     <t>00038000000</t>
+  </si>
+  <si>
+    <t>b9e6c48283f17c3c</t>
+  </si>
+  <si>
+    <t>002416531b391e3f</t>
+  </si>
+  <si>
+    <t>071c0000000</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1014,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1030,7 +1039,6 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2883,37 +2891,37 @@
       <c r="A16" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="H16" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="L16" s="16" t="s">
+      <c r="H16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2997,17 +3005,39 @@
       <c r="A19" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="12"/>
+      <c r="B19" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L19" s="12" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">

--- a/- Hash Perceptual.xlsx
+++ b/- Hash Perceptual.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3847AE68-66B9-4BDF-84B1-856B154D3E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021F98ED-81A8-4FB1-9A4F-3269AE73125B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="303">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -808,9 +808,6 @@
     <t>Alternative (29)</t>
   </si>
   <si>
-    <t>Alternative (30)</t>
-  </si>
-  <si>
     <t>402416531b191a1b</t>
   </si>
   <si>
@@ -896,13 +893,70 @@
   </si>
   <si>
     <t>071c0000000</t>
+  </si>
+  <si>
+    <t>ffffc78b0b000000</t>
+  </si>
+  <si>
+    <t>002436531b391a3f</t>
+  </si>
+  <si>
+    <t>8e2e4d2938f4f626</t>
+  </si>
+  <si>
+    <t>131b492d1d9c9f1e</t>
+  </si>
+  <si>
+    <t>6c2d3f2627cf874e</t>
+  </si>
+  <si>
+    <t>4c27236171799b99</t>
+  </si>
+  <si>
+    <t>00018000280</t>
+  </si>
+  <si>
+    <t>ffffc7cb0b000000</t>
+  </si>
+  <si>
+    <t>0003a000000</t>
+  </si>
+  <si>
+    <t>2000200020103204</t>
+  </si>
+  <si>
+    <t>ffffc7cf0b000200</t>
+  </si>
+  <si>
+    <t>402416531b391a3f</t>
+  </si>
+  <si>
+    <t>00000000101</t>
+  </si>
+  <si>
+    <t>b9e6c68283f15c3c</t>
+  </si>
+  <si>
+    <t>002416531b399a3e</t>
+  </si>
+  <si>
+    <t>08043001000</t>
+  </si>
+  <si>
+    <t>b9c4d65a8bd15c34</t>
+  </si>
+  <si>
+    <t>08092001000</t>
+  </si>
+  <si>
+    <t>09086001000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -924,14 +978,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -980,12 +1028,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1014,7 +1056,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1035,9 +1077,6 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2302,18 +2341,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977491FD-2608-4368-88A1-010C2609C8BB}">
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2442,19 +2481,19 @@
         <v>211</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>215</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>35</v>
@@ -2480,16 +2519,16 @@
         <v>211</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>215</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>223</v>
@@ -2524,7 +2563,7 @@
         <v>215</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>213</v>
@@ -2556,16 +2595,16 @@
         <v>211</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>215</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>35</v>
@@ -2594,7 +2633,7 @@
         <v>211</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>215</v>
@@ -2629,7 +2668,7 @@
         <v>208</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>213</v>
@@ -2638,7 +2677,7 @@
         <v>215</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>213</v>
@@ -2673,10 +2712,10 @@
         <v>213</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>213</v>
@@ -2708,16 +2747,16 @@
         <v>211</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>35</v>
@@ -2746,16 +2785,16 @@
         <v>211</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>215</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>35</v>
@@ -2784,16 +2823,16 @@
         <v>211</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>215</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>35</v>
@@ -2819,19 +2858,19 @@
         <v>208</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>215</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>35</v>
@@ -2860,16 +2899,16 @@
         <v>210</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>35</v>
@@ -2904,7 +2943,7 @@
         <v>215</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>212</v>
@@ -2939,10 +2978,10 @@
         <v>213</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>213</v>
@@ -2968,22 +3007,22 @@
         <v>241</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>35</v>
@@ -3006,27 +3045,27 @@
         <v>242</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C19" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>284</v>
-      </c>
       <c r="G19" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I19" s="2" t="s">
+      <c r="I19" s="1" t="s">
         <v>35</v>
       </c>
       <c r="J19" s="1" t="s">
@@ -3035,7 +3074,7 @@
       <c r="K19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L19" s="12" t="s">
+      <c r="L19" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3043,53 +3082,75 @@
       <c r="A20" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="12"/>
+      <c r="B20" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>244</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L21" s="2" t="s">
+      <c r="G21" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3097,193 +3158,380 @@
       <c r="A22" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="12"/>
+      <c r="B22" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="12"/>
+      <c r="B23" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="12"/>
+      <c r="B24" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="12"/>
+      <c r="B25" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="12"/>
+      <c r="B26" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F26" s="1">
+        <v>13640001000</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="12"/>
+      <c r="B27" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="12"/>
+      <c r="B28" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F28" s="1">
+        <v>11047000000</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="12"/>
+      <c r="B29" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="12"/>
+      <c r="B30" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F30" s="1">
+        <v>11043001000</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="12"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="B31" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="12"/>
-    </row>
-    <row r="36" spans="1:5" ht="24" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="D36" s="15" t="s">
+      <c r="E31" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E36" s="15">
-        <v>8091001000</v>
+      <c r="F31" s="1">
+        <v>13480002000</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/- Hash Perceptual.xlsx
+++ b/- Hash Perceptual.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021F98ED-81A8-4FB1-9A4F-3269AE73125B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F3A4DDE-6693-4069-A49D-DB589EDDC6A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="2" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="22" r:id="rId1"/>
     <sheet name="MountainDatabase" sheetId="23" r:id="rId2"/>
-    <sheet name="WashingtonDatabase" sheetId="2" r:id="rId3"/>
+    <sheet name="PalaceDatabase" sheetId="24" r:id="rId3"/>
+    <sheet name="WashingtonDatabase" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">LennaDatabase!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">LennaDatabase!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="316">
   <si>
     <t>Imagem Original</t>
   </si>
@@ -950,6 +951,45 @@
   </si>
   <si>
     <t>09086001000</t>
+  </si>
+  <si>
+    <t>Alternative (30)</t>
+  </si>
+  <si>
+    <t>ffffe7e080000000</t>
+  </si>
+  <si>
+    <t>f5a5854f4a60b725</t>
+  </si>
+  <si>
+    <t>e6ce8e991c149694</t>
+  </si>
+  <si>
+    <t>ffffe7e080860242</t>
+  </si>
+  <si>
+    <t>e3eecece8c1a7e16</t>
+  </si>
+  <si>
+    <t>9ececc9cded2d2ce</t>
+  </si>
+  <si>
+    <t>edfbfbeefcffdfdf</t>
+  </si>
+  <si>
+    <t>1707070707270606</t>
+  </si>
+  <si>
+    <t>00000007</t>
+  </si>
+  <si>
+    <t>e6ce8e893c149694</t>
+  </si>
+  <si>
+    <t>7c7ce8e8f8fce989</t>
+  </si>
+  <si>
+    <t>3ffffcf4f4f4f5e4</t>
   </si>
 </sst>
 </file>
@@ -3541,6 +3581,570 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35545A2-076D-4EF6-A5CE-8905072E548B}">
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="F3" s="2">
+        <v>19000240</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D97718C6-A416-40C3-8D45-6453EFA375E9}">
   <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
